--- a/config/auto_configs/2015_Hyundai_Hyundai_Tucson FCEV(LM FCEV)_100kW.xlsx
+++ b/config/auto_configs/2015_Hyundai_Hyundai_Tucson FCEV(LM FCEV)_100kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_00283</t>
+          <t>HMA_002B3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>C1616</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>SRS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_002B3</t>
+          <t>HMA_00283</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C1616</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -578,6 +578,402 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TPMS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HMA_002E4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HMA_002C0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AHB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HMA_00304</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BCM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HMA_002BC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HMA_00312</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BPCU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HMA_002B5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HMA_002CD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCU</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HMA_002F8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FPD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HMA_002F7</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HDC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HMA_002C3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HSCU</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HMA_002E2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LDC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HMA_002F6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MCU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HMA_002E5</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PDM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HMA_0022E</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SJB</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HMA_00314</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SKCS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>HMA_0012C</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HMA_002FE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HMA_002E0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>00</t>
         </is>
